--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.59580749133845</v>
+        <v>3.346818717342499</v>
       </c>
       <c r="D2" t="n">
-        <v>20.47873977470454</v>
+        <v>3.327795213389488</v>
       </c>
       <c r="E2" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F2" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.99427670508019</v>
+        <v>2.43656996457553</v>
       </c>
       <c r="D3" t="n">
-        <v>15.12326585590008</v>
+        <v>2.457530701583763</v>
       </c>
       <c r="E3" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F3" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.83715977533388</v>
+        <v>3.223538463491756</v>
       </c>
       <c r="D4" t="n">
-        <v>19.93278198731033</v>
+        <v>3.239077072937929</v>
       </c>
       <c r="E4" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F4" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.7345434353871</v>
+        <v>5.156863308250403</v>
       </c>
       <c r="D5" t="n">
-        <v>31.84590837976918</v>
+        <v>5.174960111712491</v>
       </c>
       <c r="E5" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F5" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.59731180309032</v>
+        <v>3.347063168002178</v>
       </c>
       <c r="D6" t="n">
-        <v>20.68660908660015</v>
+        <v>3.361573976572525</v>
       </c>
       <c r="E6" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F6" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.69490718008191</v>
+        <v>9.050422416763311</v>
       </c>
       <c r="D7" t="n">
-        <v>55.85990358508364</v>
+        <v>9.077234332576092</v>
       </c>
       <c r="E7" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F7" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>67.77063900207409</v>
+        <v>11.01272883783704</v>
       </c>
       <c r="D8" t="n">
-        <v>67.89734514767395</v>
+        <v>11.03331858649702</v>
       </c>
       <c r="E8" t="n">
-        <v>19.01430822126326</v>
+        <v>3.08982508595528</v>
       </c>
       <c r="F8" t="n">
-        <v>19.0501820554077</v>
+        <v>3.095654584003751</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
